--- a/artfynd/A 22712-2021 artfynd.xlsx
+++ b/artfynd/A 22712-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118957921</v>
+        <v>118957825</v>
       </c>
       <c r="B2" t="n">
         <v>102892</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -731,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>618309</v>
+        <v>618285</v>
       </c>
       <c r="R2" t="n">
-        <v>6561285</v>
+        <v>6561231</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -771,7 +771,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På hygge från vintern -23. Var inte alls runt på hela hygget.</t>
+          <t>På hygge från vintern -23. Högt med piprör runtom där det inte markberetts.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118930358</v>
+        <v>118957921</v>
       </c>
       <c r="B3" t="n">
         <v>102892</v>
@@ -834,7 +834,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -858,10 +858,10 @@
         <v>618309</v>
       </c>
       <c r="R3" t="n">
-        <v>6561159</v>
+        <v>6561285</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På hygge från vintern -23. Av de 20 var 4 plantor klart annorlunda, infertila. Bara sett en gång förut tror jag.</t>
+          <t>På hygge från vintern -23. Var inte alls runt på hela hygget.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118957825</v>
+        <v>118930358</v>
       </c>
       <c r="B4" t="n">
         <v>102892</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -979,13 +979,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>618285</v>
+        <v>618309</v>
       </c>
       <c r="R4" t="n">
-        <v>6561231</v>
+        <v>6561159</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På hygge från vintern -23. Högt med piprör runtom där det inte markberetts.</t>
+          <t>På hygge från vintern -23. Av de 20 var 4 plantor klart annorlunda, infertila. Bara sett en gång förut tror jag.</t>
         </is>
       </c>
       <c r="AD4" t="b">
